--- a/templates/ht_cn/hetong-Footer.xlsx
+++ b/templates/ht_cn/hetong-Footer.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>合计 Total</t>
   </si>
@@ -442,10 +442,32 @@
     <t>杨燕如</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>签字日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>205-11-14</t>
+  </si>
+  <si>
     <t>签字日期:</t>
-  </si>
-  <si>
-    <t>205-11-14</t>
   </si>
   <si>
     <t>公章（盖章处）:</t>
@@ -464,7 +486,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +525,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1031,137 +1060,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1192,8 +1221,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1302,41 +1334,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>774700</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>565785</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>81280</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="香港盖章"/>
+        <xdr:cNvPr id="4" name="图片 3" descr="中国公司盖章"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="21360000">
-          <a:off x="3194050" y="5130800"/>
-          <a:ext cx="2813685" cy="1427480"/>
+        <a:xfrm>
+          <a:off x="4108450" y="4638675"/>
+          <a:ext cx="2495550" cy="2308225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1915,7 +1944,7 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" ht="26" spans="1:8">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="12" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -1924,7 +1953,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="3"/>
       <c r="E29" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>41</v>
@@ -1934,7 +1963,7 @@
     </row>
     <row r="30" ht="26" spans="1:8">
       <c r="A30" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>1</v>
@@ -1942,7 +1971,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="3"/>
       <c r="E30" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>1</v>
@@ -1951,13 +1980,13 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="13" t="s">
         <v>1</v>
       </c>
       <c r="F31" s="2"/>
@@ -1965,13 +1994,13 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="13" t="s">
         <v>1</v>
       </c>
       <c r="F32" s="2"/>
@@ -1979,13 +2008,13 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="13" t="s">
         <v>1</v>
       </c>
       <c r="F33" s="2"/>
@@ -1993,8 +2022,8 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="13" t="s">
-        <v>43</v>
+      <c r="A34" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ht_cn/hetong-Footer.xlsx
+++ b/templates/ht_cn/hetong-Footer.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t>合计 Total</t>
   </si>
@@ -412,54 +412,36 @@
     <t>HONG KONG UNICORN TECHNOLOGY LIMITED</t>
   </si>
   <si>
-    <r>
-      <rPr>
+    <t>深圳市盛芯烁科技有限公司</t>
+  </si>
+  <si>
+    <t>授权代表:</t>
+  </si>
+  <si>
+    <t>Joy Kim</t>
+  </si>
+  <si>
+    <t>贝伟航</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF333333"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>深圳欣亿扬微科技有限公司</t>
-    </r>
-    <r>
-      <rPr>
+      <t>签字日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF333333"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>授权代表:</t>
-  </si>
-  <si>
-    <t>Joy Kim</t>
-  </si>
-  <si>
-    <t>杨燕如</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>签字日期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>:</t>
     </r>
   </si>
@@ -468,6 +450,9 @@
   </si>
   <si>
     <t>签字日期:</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
   </si>
   <si>
     <t>公章（盖章处）:</t>
@@ -1328,44 +1313,6 @@
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3" descr="中国公司盖章"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4108450" y="4638675"/>
-          <a:ext cx="2495550" cy="2308225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1956,14 +1903,14 @@
         <v>42</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" ht="26" spans="1:8">
       <c r="A30" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>1</v>
@@ -1971,7 +1918,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="3"/>
       <c r="E30" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>1</v>
@@ -2023,7 +1970,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
